--- a/output/full_scan/batch_seq6_2026-07-15.xlsx
+++ b/output/full_scan/batch_seq6_2026-07-15.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O116"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6464</v>
+        <v>6226</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>959.0195039608842</v>
+        <v>978.9937371649936</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>78.7</v>
+        <v>27.8</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>62.21211531056239</v>
+        <v>76.06088462219041</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>24.05508848167127</v>
+        <v>40.21926965098408</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4.501950396088426</v>
+        <v>0.4479149866775787</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,48 +570,48 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0727264628856743</v>
+        <v>0.5179785483346562</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6288</v>
+        <v>6464</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>聯嘉</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>933.7637113435804</v>
+        <v>959.0195039608842</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>24.25</v>
+        <v>78.7</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>66.55514051006455</v>
+        <v>62.21211531056239</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>25.22091608319549</v>
+        <v>24.05508848167127</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.476371134358034</v>
+        <v>4.501950396088426</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
@@ -623,51 +623,51 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1990034752269772</v>
+        <v>0.0727264628856743</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6241</v>
+        <v>6288</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>聯嘉</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>788.0920747930645</v>
+        <v>933.7637113435804</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>18.8</v>
+        <v>24.25</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>80.31597939262821</v>
+        <v>66.55514051006455</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>44.97264760239474</v>
+        <v>25.22091608319549</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.409207479306447</v>
+        <v>3.476371134358034</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2238651892257896</v>
+        <v>0.1990034752269772</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6446</v>
+        <v>6241</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>741.2419875534024</v>
+        <v>788.0920747930645</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1320</v>
+        <v>18.8</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>58.73080525930353</v>
+        <v>80.31597939262821</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45.68373304472333</v>
+        <v>44.97264760239474</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.6718994335238911</v>
+        <v>2.409207479306447</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-20.18378909013467</v>
+        <v>0.2238651892257896</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6409</v>
+        <v>6446</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>730.2039188463139</v>
+        <v>741.2419875534024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1080</v>
+        <v>1320</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>55.84507119982645</v>
+        <v>58.73080525930353</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>43.42908255471162</v>
+        <v>45.68373304472333</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.5037714053500923</v>
+        <v>0.6718994335238911</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-13.11239235585965</v>
+        <v>-20.18378909013467</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6202</v>
+        <v>6409</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>703.3705528743436</v>
+        <v>730.2039188463139</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>1080</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>56.89609383111358</v>
+        <v>55.84507119982645</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>27.32465907964744</v>
+        <v>43.42908255471162</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.8004074290838531</v>
+        <v>0.5037714053500923</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.0235148971220793</v>
+        <v>-13.11239235585965</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6270</v>
+        <v>6202</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>700.7790581235788</v>
+        <v>703.3705528743436</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>34.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>46.6233785007846</v>
+        <v>56.89609383111358</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>42.46880798356585</v>
+        <v>27.32465907964744</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.2746232811770619</v>
+        <v>0.8004074290838531</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.853127245308007</v>
+        <v>-0.0235148971220793</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6416</v>
+        <v>6270</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>678.1853055141601</v>
+        <v>700.7790581235788</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>101.5</v>
+        <v>34.2</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>76.11354829370885</v>
+        <v>46.6233785007846</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>30.48224547055068</v>
+        <v>42.46880798356585</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.418530551416006</v>
+        <v>0.2746232811770619</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>2.255829108667263</v>
+        <v>-0.853127245308007</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6165</v>
+        <v>6416</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>670.7342812324576</v>
+        <v>678.1853055141601</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>50.9</v>
+        <v>101.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>58.79256016838117</v>
+        <v>76.11354829370885</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>21.17352122896748</v>
+        <v>30.48224547055068</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.7327337970931933</v>
+        <v>1.418530551416006</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2781246502482068</v>
+        <v>2.255829108667263</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6472</v>
+        <v>6165</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>663.920989071504</v>
+        <v>670.7342812324576</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>428.5</v>
+        <v>50.9</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>55.29499860030006</v>
+        <v>58.79256016838117</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>30.86768741955183</v>
+        <v>21.17352122896748</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.6810626989614434</v>
+        <v>0.7327337970931933</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-1.913504081431554</v>
+        <v>0.2781246502482068</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6477</v>
+        <v>6472</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>628.9833813665558</v>
+        <v>663.920989071504</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>42.2</v>
+        <v>428.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>68.55500980840245</v>
+        <v>55.29499860030006</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>28.63681643160513</v>
+        <v>30.86768741955183</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.998338136655581</v>
+        <v>0.6810626989614434</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.9992473985604884</v>
+        <v>-1.913504081431554</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6196</v>
+        <v>6477</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>626.1329515888642</v>
+        <v>628.9833813665558</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>585</v>
+        <v>42.2</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>61.65100792396216</v>
+        <v>68.55500980840245</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>23.93977001093064</v>
+        <v>28.63681643160513</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.14231499396634</v>
+        <v>1.998338136655581</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-4.066553252796055</v>
+        <v>0.9992473985604884</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6197</v>
+        <v>6196</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>594.3811386332462</v>
+        <v>626.1329515888642</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>334.5</v>
+        <v>585</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>49.54212754194764</v>
+        <v>61.65100792396216</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>33.55364425852989</v>
+        <v>23.93977001093064</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.6201839658154926</v>
+        <v>1.14231499396634</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-7.43342075274175</v>
+        <v>-4.066553252796055</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6432</v>
+        <v>6197</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>590.5108431624707</v>
+        <v>594.3811386332462</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>73.7</v>
+        <v>334.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>51.24825920719979</v>
+        <v>49.54212754194764</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>25.12445880831413</v>
+        <v>33.55364425852989</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.3545703769350811</v>
+        <v>0.6201839658154926</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-1.247785292365434</v>
+        <v>-7.43342075274175</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6414</v>
+        <v>6432</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>589.9505530779694</v>
+        <v>590.5108431624707</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>394.5</v>
+        <v>73.7</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>57.67582147077037</v>
+        <v>51.24825920719979</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>18.42327643732353</v>
+        <v>25.12445880831413</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.076107556698445</v>
+        <v>0.3545703769350811</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.3657304731543487</v>
+        <v>-1.247785292365434</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6274</v>
+        <v>6414</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>573.4466763656635</v>
+        <v>589.9505530779694</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1435</v>
+        <v>394.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>42.69221912585382</v>
+        <v>57.67582147077037</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>20.50356479039579</v>
+        <v>18.42327643732353</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.016681626674639</v>
+        <v>1.076107556698445</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-41.4987927066683</v>
+        <v>0.3657304731543487</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6220</v>
+        <v>6274</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>556.5506131624599</v>
+        <v>573.4466763656635</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>35</v>
+        <v>1435</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>51.16164885323219</v>
+        <v>42.69221912585382</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>36.11244612296345</v>
+        <v>20.50356479039579</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.499870302356167</v>
+        <v>1.016681626674639</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.1842883529863803</v>
+        <v>-41.4987927066683</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6177</v>
+        <v>6220</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>552.6533519219442</v>
+        <v>556.5506131624599</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>46.9</v>
+        <v>35</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>56.59514332392524</v>
+        <v>51.16164885323219</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>19.52232619224369</v>
+        <v>36.11244612296345</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.7173718058065597</v>
+        <v>0.499870302356167</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.0289092040632096</v>
+        <v>-0.1842883529863803</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6257</v>
+        <v>6177</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>552.0650915624524</v>
+        <v>552.6533519219442</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>237.5</v>
+        <v>46.9</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>51.79960048079918</v>
+        <v>56.59514332392524</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>19.73030289027401</v>
+        <v>19.52232619224369</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.5736767620823198</v>
+        <v>0.7173718058065597</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-2.245052156913492</v>
+        <v>0.0289092040632096</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6223</v>
+        <v>6257</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>547.1618455059535</v>
+        <v>552.0650915624524</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>6330</v>
+        <v>237.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>48.69611008195365</v>
+        <v>51.79960048079918</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>23.32489663814706</v>
+        <v>19.73030289027401</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.8331728920454932</v>
+        <v>0.5736767620823198</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-78.24336911749108</v>
+        <v>-2.245052156913492</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6235</v>
+        <v>6223</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>532.2159083927376</v>
+        <v>547.1618455059535</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>44.2</v>
+        <v>6330</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>56.30606367965421</v>
+        <v>48.69611008195365</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20.86160290832251</v>
+        <v>23.32489663814706</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.9620628745972428</v>
+        <v>0.8331728920454932</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.2786720892557504</v>
+        <v>-78.24336911749108</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6284</v>
+        <v>6235</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>530.4982480037947</v>
+        <v>532.2159083927376</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>92.3</v>
+        <v>44.2</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>42.17874130410723</v>
+        <v>56.30606367965421</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>26.60017055220388</v>
+        <v>20.86160290832251</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.7436263839708164</v>
+        <v>0.9620628745972428</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-1.534618318950984</v>
+        <v>0.2786720892557504</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6187</v>
+        <v>6284</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>524.4446985192409</v>
+        <v>530.4982480037947</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1080</v>
+        <v>92.3</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,49 +1718,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>51.41672857249201</v>
+        <v>42.17874130410723</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>9.661668116943106</v>
+        <v>26.60017055220388</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.9050733911313</v>
+        <v>0.7436263839708164</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.8373656278900228</v>
+        <v>-1.534618318950984</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6175</v>
+        <v>6187</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>520.8476741984251</v>
+        <v>524.4446985192409</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>103</v>
+        <v>1080</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>49.03368947018955</v>
+        <v>51.41672857249201</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>30.13497116212208</v>
+        <v>9.661668116943106</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.3677367764124216</v>
+        <v>0.9050733911313</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-2.19138372729625</v>
+        <v>0.8373656278900228</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6259</v>
+        <v>6175</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>513.3588711341471</v>
+        <v>520.8476741984251</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>36.65</v>
+        <v>103</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>52.89903309373591</v>
+        <v>49.03368947018955</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>33.41883610348986</v>
+        <v>30.13497116212208</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.7769879440296835</v>
+        <v>0.3677367764124216</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.6462974329084439</v>
+        <v>-2.19138372729625</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6243</v>
+        <v>6259</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>504.7289310887872</v>
+        <v>513.3588711341471</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>43.6</v>
+        <v>36.65</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>61.77087149008501</v>
+        <v>52.89903309373591</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>26.40508650590357</v>
+        <v>33.41883610348986</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.6212815421811994</v>
+        <v>0.7769879440296835</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.1011005755248444</v>
+        <v>-0.6462974329084439</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6419</v>
+        <v>6243</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>503.3756168430342</v>
+        <v>504.7289310887872</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>147</v>
+        <v>43.6</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>52.0284687770214</v>
+        <v>61.77087149008501</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>9.19081137061163</v>
+        <v>26.40508650590357</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7205689898477657</v>
+        <v>0.6212815421811994</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.221337833857068</v>
+        <v>-0.1011005755248444</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6225</v>
+        <v>6419</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>499.1132821010656</v>
+        <v>503.3756168430342</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>26.3</v>
+        <v>147</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>63.12738777436106</v>
+        <v>52.0284687770214</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>14.3019953967378</v>
+        <v>9.19081137061163</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7437284361017755</v>
+        <v>0.7205689898477657</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.4865889812572281</v>
+        <v>-0.221337833857068</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6209</v>
+        <v>6225</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>498.6197328053139</v>
+        <v>499.1132821010656</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>78.3</v>
+        <v>26.3</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>45.69669004960313</v>
+        <v>63.12738777436106</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>23.03529312347378</v>
+        <v>14.3019953967378</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.2564105576151219</v>
+        <v>0.7437284361017755</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.8772821395984352</v>
+        <v>0.4865889812572281</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6207</v>
+        <v>6209</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>494.8883803809761</v>
+        <v>498.6197328053139</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>148.5</v>
+        <v>78.3</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>54.95272536451873</v>
+        <v>45.69669004960313</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>39.9580055370765</v>
+        <v>23.03529312347378</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.7181105764975957</v>
+        <v>0.2564105576151219</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-3.071141912503419</v>
+        <v>-0.8772821395984352</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6245</v>
+        <v>6207</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>494.4254943300199</v>
+        <v>494.8883803809761</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>82.8</v>
+        <v>148.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>53.55718401469683</v>
+        <v>54.95272536451873</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>10.5720969040761</v>
+        <v>39.9580055370765</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.461416823758166</v>
+        <v>0.7181105764975957</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.2360600710602322</v>
+        <v>-3.071141912503419</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6423</v>
+        <v>6245</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>494.3320123757258</v>
+        <v>494.4254943300199</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>73.8</v>
+        <v>82.8</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>34.53498058351718</v>
+        <v>53.55718401469683</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>24.97457830366952</v>
+        <v>10.5720969040761</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4444586672128209</v>
+        <v>1.461416823758166</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.1658371522343888</v>
+        <v>0.2360600710602322</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6281</v>
+        <v>6423</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>493.4714298995575</v>
+        <v>494.3320123757258</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>51.8</v>
+        <v>73.8</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>53.84439039612369</v>
+        <v>34.53498058351718</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>11.08366644861653</v>
+        <v>24.97457830366952</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.9077006180868276</v>
+        <v>0.4444586672128209</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0059127076142115</v>
+        <v>-0.1658371522343888</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, williams_r_recovery, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6190</v>
+        <v>6281</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>484.1374538407292</v>
+        <v>493.4714298995575</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>51.8</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>44.58671224660071</v>
+        <v>53.84439039612369</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17.07664271428304</v>
+        <v>11.08366644861653</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.6689220613586921</v>
+        <v>0.9077006180868276</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.9560653177658068</v>
+        <v>0.0059127076142115</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6182</v>
+        <v>6190</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>478.7435914719945</v>
+        <v>484.1374538407292</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>179.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>70.80524521775185</v>
+        <v>44.58671224660071</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>43.44858461629758</v>
+        <v>17.07664271428304</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.077956919553266</v>
+        <v>0.6689220613586921</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>3.64613712327926</v>
+        <v>-0.9560653177658068</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6173</v>
+        <v>6182</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>473.9085141182012</v>
+        <v>478.7435914719945</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>231.5</v>
+        <v>179.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>41.9120060855737</v>
+        <v>70.80524521775185</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>26.31768799895558</v>
+        <v>43.44858461629758</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.9108766707462136</v>
+        <v>1.077956919553266</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-13.98642881189114</v>
+        <v>3.64613712327926</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6282</v>
+        <v>6173</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>468.2978356980758</v>
+        <v>473.9085141182012</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>56.2</v>
+        <v>231.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,49 +2460,49 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>46.98610323122846</v>
+        <v>41.9120060855737</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>19.96702483064976</v>
+        <v>26.31768799895558</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.5365296755095472</v>
+        <v>0.9108766707462136</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.380973168789266</v>
+        <v>-13.98642881189114</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6191</v>
+        <v>6282</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>462.7936881335143</v>
+        <v>468.2978356980758</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>56.2</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>43.76495456840166</v>
+        <v>46.98610323122846</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>24.24494535932209</v>
+        <v>19.96702483064976</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.2418603477795949</v>
+        <v>0.5365296755095472</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-1.032118856932671</v>
+        <v>-0.380973168789266</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6277</v>
+        <v>6191</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>460.2341940722682</v>
+        <v>462.7936881335143</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>74.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>59.06717764196074</v>
+        <v>43.76495456840166</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>26.65674053063855</v>
+        <v>24.24494535932209</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.9300666020004992</v>
+        <v>0.2418603477795949</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.5449062518965896</v>
+        <v>-1.032118856932671</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6271</v>
+        <v>6277</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>455.0574742265688</v>
+        <v>460.2341940722682</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>224</v>
+        <v>74.3</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>43.84774980810717</v>
+        <v>59.06717764196074</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>21.17059566996729</v>
+        <v>26.65674053063855</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.4319207132470264</v>
+        <v>0.9300666020004992</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-6.166812761616894</v>
+        <v>0.5449062518965896</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6285</v>
+        <v>6271</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>451.12965686595</v>
+        <v>455.0574742265688</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>52.77200023019674</v>
+        <v>43.84774980810717</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16.28378475865673</v>
+        <v>21.17059566996729</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.077942706641323</v>
+        <v>0.4319207132470264</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.183588317675711</v>
+        <v>-6.166812761616894</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6418</v>
+        <v>6285</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>448.928901148897</v>
+        <v>451.12965686595</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>33</v>
+        <v>267</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>53.61849167717919</v>
+        <v>52.77200023019674</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>20.40614660690978</v>
+        <v>16.28378475865673</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.4263101967919093</v>
+        <v>1.077942706641323</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0163249562232002</v>
+        <v>1.183588317675711</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6266</v>
+        <v>6418</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>446.8082884780436</v>
+        <v>448.928901148897</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>26.1</v>
+        <v>33</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>51.85164926476324</v>
+        <v>53.61849167717919</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>17.55150110976667</v>
+        <v>20.40614660690978</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.098253715119315</v>
+        <v>0.4263101967919093</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>1</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1586548730844746</v>
+        <v>0.0163249562232002</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6166</v>
+        <v>6266</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>446.048222501837</v>
+        <v>446.8082884780436</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>129.5</v>
+        <v>26.1</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>46.24025603603876</v>
+        <v>51.85164926476324</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>30.9561972153387</v>
+        <v>17.55150110976667</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.3557170320691451</v>
+        <v>1.098253715119315</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-2.180782961939123</v>
+        <v>0.1586548730844746</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6204</v>
+        <v>6166</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>445.9245600546281</v>
+        <v>446.048222501837</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>86.2</v>
+        <v>129.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>34.21057645701964</v>
+        <v>46.24025603603876</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>28.77386880688399</v>
+        <v>30.9561972153387</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.3605538445693569</v>
+        <v>0.3557170320691451</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-4.882339689879421</v>
+        <v>-2.180782961939123</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6214</v>
+        <v>6204</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>445.9164532931849</v>
+        <v>445.9245600546281</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>141</v>
+        <v>86.2</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>56.79642046252405</v>
+        <v>34.21057645701964</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15.45117205805954</v>
+        <v>28.77386880688399</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4275729786557311</v>
+        <v>0.3605538445693569</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.7411264080137274</v>
+        <v>-4.882339689879421</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6265</v>
+        <v>6214</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>438.7559679325241</v>
+        <v>445.9164532931849</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>53.8</v>
+        <v>141</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>51.78693347812966</v>
+        <v>56.79642046252405</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>16.01092352794289</v>
+        <v>15.45117205805954</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.7774425524018422</v>
+        <v>0.4275729786557311</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.2146313018472391</v>
+        <v>0.7411264080137274</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6213</v>
+        <v>6265</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>431.810204172593</v>
+        <v>438.7559679325241</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>335</v>
+        <v>53.8</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>51.09617951580636</v>
+        <v>51.78693347812966</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>23.50926890841757</v>
+        <v>16.01092352794289</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.7515443756919248</v>
+        <v>0.7774425524018422</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-3.816917331211286</v>
+        <v>-0.2146313018472391</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6192</v>
+        <v>6213</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>431.0207997412398</v>
+        <v>431.810204172593</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>120.5</v>
+        <v>335</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>48.385751201441</v>
+        <v>51.09617951580636</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>19.73436750645985</v>
+        <v>23.50926890841757</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4341782071704106</v>
+        <v>0.7515443756919248</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.1399841963359351</v>
+        <v>-3.816917331211286</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6435</v>
+        <v>6192</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>430.1060105298288</v>
+        <v>431.0207997412398</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>324.5</v>
+        <v>120.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>47.56519047064712</v>
+        <v>48.385751201441</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>29.98314640454748</v>
+        <v>19.73436750645985</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.4106010529828777</v>
+        <v>0.4341782071704106</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-8.349227475102381</v>
+        <v>0.1399841963359351</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6451</v>
+        <v>6435</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>427.4035694576828</v>
+        <v>430.1060105298288</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>491</v>
+        <v>324.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>43.96522117188876</v>
+        <v>47.56519047064712</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>20.53057818540613</v>
+        <v>29.98314640454748</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4593069943309536</v>
+        <v>0.4106010529828777</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-10.8482733708987</v>
+        <v>-8.349227475102381</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6215</v>
+        <v>6451</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>420.3894982991923</v>
+        <v>427.4035694576828</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>105</v>
+        <v>491</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>42.97615262414244</v>
+        <v>43.96522117188876</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>16.23198513044738</v>
+        <v>20.53057818540613</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3074309952166655</v>
+        <v>0.4593069943309536</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0690288383667467</v>
+        <v>-10.8482733708987</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6201</v>
+        <v>6215</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>420.2723879228962</v>
+        <v>420.3894982991923</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>49.2</v>
+        <v>105</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>56.46991130540984</v>
+        <v>42.97615262414244</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>10.58344649016731</v>
+        <v>16.23198513044738</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.110322130811792</v>
+        <v>0.3074309952166655</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0969847075478257</v>
+        <v>0.0690288383667467</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6278</v>
+        <v>6201</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>398.9437173549255</v>
+        <v>420.2723879228962</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>177</v>
+        <v>49.2</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>39.1406671201003</v>
+        <v>56.46991130540984</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>17.26223107119822</v>
+        <v>10.58344649016731</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.6773673026722372</v>
+        <v>1.110322130811792</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-3.724831345392368</v>
+        <v>0.0969847075478257</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6183</v>
+        <v>6278</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>397.8233106200191</v>
+        <v>398.9437173549255</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>177</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>56.95501106613694</v>
+        <v>39.1406671201003</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>14.79710053640692</v>
+        <v>17.26223107119822</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.9462990214645955</v>
+        <v>0.6773673026722372</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.1713542213307619</v>
+        <v>-3.724831345392368</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6185</v>
+        <v>6183</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>388.1621367169595</v>
+        <v>397.8233106200191</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>14.25</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>49.06247627305773</v>
+        <v>56.95501106613694</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>18.51911101457774</v>
+        <v>14.79710053640692</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5124917732933324</v>
+        <v>0.9462990214645955</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0325424981731389</v>
+        <v>0.1713542213307619</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6438</v>
+        <v>6185</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>382.1074029663922</v>
+        <v>388.1621367169595</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>154</v>
+        <v>14.25</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>47.79038261056867</v>
+        <v>49.06247627305773</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>18.93673326150845</v>
+        <v>18.51911101457774</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.6237943317046015</v>
+        <v>0.5124917732933324</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.34119879062697</v>
+        <v>-0.0325424981731389</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6168</v>
+        <v>6438</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>378.6090753726614</v>
+        <v>382.1074029663922</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>27.6</v>
+        <v>154</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>45.58016392771468</v>
+        <v>47.79038261056867</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>21.06382508000081</v>
+        <v>18.93673326150845</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.3114471132127022</v>
+        <v>0.6237943317046015</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.485331845483498</v>
+        <v>-0.34119879062697</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6261</v>
+        <v>6168</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>374.8971923064378</v>
+        <v>378.6090753726614</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>90.2</v>
+        <v>27.6</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>40.05455411715</v>
+        <v>45.58016392771468</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>19.22214536125998</v>
+        <v>21.06382508000081</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.4140359131227321</v>
+        <v>0.3114471132127022</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.0506254228001585</v>
+        <v>-0.485331845483498</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6224</v>
+        <v>6261</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>368.8607505901002</v>
+        <v>374.8971923064378</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>64.5</v>
+        <v>90.2</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>38.11711061851899</v>
+        <v>40.05455411715</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>17.27030652848985</v>
+        <v>19.22214536125998</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.3148089242528703</v>
+        <v>0.4140359131227321</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-1.863622288244054</v>
+        <v>-0.0506254228001585</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6279</v>
+        <v>6224</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>368.4788546699716</v>
+        <v>368.8607505901002</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>120</v>
+        <v>64.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>49.64222407997885</v>
+        <v>38.11711061851899</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>18.97370205745138</v>
+        <v>17.27030652848985</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.549797261898764</v>
+        <v>0.3148089242528703</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.0435853123989044</v>
+        <v>-1.863622288244054</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6164</v>
+        <v>6279</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>364.7656674849816</v>
+        <v>368.4788546699716</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>13.9</v>
+        <v>120</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.78871893812994</v>
+        <v>49.64222407997885</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>22.54276323914787</v>
+        <v>18.97370205745138</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3765667484981605</v>
+        <v>0.549797261898764</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.1168088971837814</v>
+        <v>-0.0435853123989044</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6208</v>
+        <v>6164</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>362.6345025790613</v>
+        <v>364.7656674849816</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>88.40000000000001</v>
+        <v>13.9</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>46.67155883193344</v>
+        <v>49.78871893812994</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>16.70516896738515</v>
+        <v>22.54276323914787</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.3762246907637954</v>
+        <v>0.3765667484981605</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-1.484759008807549</v>
+        <v>-0.1168088971837814</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6465</v>
+        <v>6208</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>362.413401216287</v>
+        <v>362.6345025790613</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>58</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>46.75730981759437</v>
+        <v>46.67155883193344</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>22.4044223036881</v>
+        <v>16.70516896738515</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.2707586097496439</v>
+        <v>0.3762246907637954</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-1.113349266313633</v>
+        <v>-1.484759008807549</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6234</v>
+        <v>6465</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>362.268060278134</v>
+        <v>362.413401216287</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>42.1</v>
+        <v>58</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>43.23407595510131</v>
+        <v>46.75730981759437</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>13.71452799126957</v>
+        <v>22.4044223036881</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.2747638425553176</v>
+        <v>0.2707586097496439</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.5203501299770925</v>
+        <v>-1.113349266313633</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6218</v>
+        <v>6234</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>362.2114666167439</v>
+        <v>362.268060278134</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>36.45</v>
+        <v>42.1</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>50.0089999496424</v>
+        <v>43.23407595510131</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>12.35980611775422</v>
+        <v>13.71452799126957</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.048257097971358</v>
+        <v>0.2747638425553176</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0314992322515517</v>
+        <v>-0.5203501299770925</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6411</v>
+        <v>6218</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>359.6244102142284</v>
+        <v>362.2114666167439</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>88.7</v>
+        <v>36.45</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>40.17023531289323</v>
+        <v>50.0089999496424</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>21.16301066867068</v>
+        <v>12.35980611775422</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3089140054023674</v>
+        <v>1.048257097971358</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-1.713479856296995</v>
+        <v>-0.0314992322515517</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6244</v>
+        <v>6411</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>350.9836184022948</v>
+        <v>359.6244102142284</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>26.7</v>
+        <v>88.7</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>44.99270096971209</v>
+        <v>40.17023531289323</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>10.64922385256134</v>
+        <v>21.16301066867068</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4353383649035767</v>
+        <v>0.3089140054023674</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0392213876411873</v>
+        <v>-1.713479856296995</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6229</v>
+        <v>6244</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>345.5245508040758</v>
+        <v>350.9836184022948</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>26.35</v>
+        <v>26.7</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>47.70920977325511</v>
+        <v>44.99270096971209</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>11.97873391755969</v>
+        <v>10.64922385256134</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.8484388502755091</v>
+        <v>0.4353383649035767</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.168612035747704</v>
+        <v>-0.0392213876411873</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6417</v>
+        <v>6229</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>344.912046454184</v>
+        <v>345.5245508040758</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>123.5</v>
+        <v>26.35</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>37.01364355434026</v>
+        <v>47.70920977325511</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>12.03114309452888</v>
+        <v>11.97873391755969</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>3.230900136300241</v>
+        <v>0.8484388502755091</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.7969871861777775</v>
+        <v>-0.168612035747704</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6198</v>
+        <v>6417</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>343.4154274546798</v>
+        <v>344.912046454184</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>20.5</v>
+        <v>123.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>50.39640846027832</v>
+        <v>37.01364355434026</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>7.946119402403495</v>
+        <v>12.03114309452888</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5210569088749506</v>
+        <v>3.230900136300241</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.026933079597871</v>
+        <v>-0.7969871861777775</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6426</v>
+        <v>6198</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>342.8506475746084</v>
+        <v>343.4154274546798</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>180</v>
+        <v>20.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>39.07498673176808</v>
+        <v>50.39640846027832</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>19.95324466064793</v>
+        <v>7.946119402403495</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4920729854809252</v>
+        <v>0.5210569088749506</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.4816663949174806</v>
+        <v>-0.026933079597871</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6239</v>
+        <v>6426</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>333.7744064758984</v>
+        <v>342.8506475746084</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>314</v>
+        <v>180</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>47.21967618626052</v>
+        <v>39.07498673176808</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>20.1879915225204</v>
+        <v>19.95324466064793</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5126224506416781</v>
+        <v>0.4920729854809252</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-5.126788694361567</v>
+        <v>-0.4816663949174806</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6263</v>
+        <v>6239</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>331.6088006630746</v>
+        <v>333.7744064758984</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>157.5</v>
+        <v>314</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>43.71332564863357</v>
+        <v>47.21967618626052</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>11.2250059201316</v>
+        <v>20.1879915225204</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.3711706415521318</v>
+        <v>0.5126224506416781</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.6515586086088682</v>
+        <v>-5.126788694361567</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6206</v>
+        <v>6263</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>329.1733726475486</v>
+        <v>331.6088006630746</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>126</v>
+        <v>157.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>44.05679983832647</v>
+        <v>43.71332564863357</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>13.36928547597672</v>
+        <v>11.2250059201316</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6800475138158321</v>
+        <v>0.3711706415521318</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.5648661263943023</v>
+        <v>-0.6515586086088682</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6442</v>
+        <v>6206</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>329.1007634928381</v>
+        <v>329.1733726475486</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>1430</v>
+        <v>126</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>37.33873206133825</v>
+        <v>44.05679983832647</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>21.67724706992493</v>
+        <v>13.36928547597672</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.909599113474334</v>
+        <v>0.6800475138158321</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-28.81590566285704</v>
+        <v>-0.5648661263943023</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6189</v>
+        <v>6442</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>327.4116403348001</v>
+        <v>329.1007634928381</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>49.6</v>
+        <v>1430</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>43.16445081082399</v>
+        <v>37.33873206133825</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>16.24162669919435</v>
+        <v>21.67724706992493</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.2070610957768766</v>
+        <v>0.909599113474334</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.4463801908009195</v>
+        <v>-28.81590566285704</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6292</v>
+        <v>6189</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>321.2255349347697</v>
+        <v>327.4116403348001</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>54.2</v>
+        <v>49.6</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>39.85131994898593</v>
+        <v>43.16445081082399</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>20.0268097358517</v>
+        <v>16.24162669919435</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.2390392361698275</v>
+        <v>0.2070610957768766</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-1.178718923010528</v>
+        <v>-0.4463801908009195</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6474</v>
+        <v>6292</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>306.6773110944108</v>
+        <v>321.2255349347697</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>37.75</v>
+        <v>54.2</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>51.49035336150448</v>
+        <v>39.85131994898593</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>12.34865928908186</v>
+        <v>20.0268097358517</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.8269373065852447</v>
+        <v>0.2390392361698275</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.1572541786013548</v>
+        <v>-1.178718923010528</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6216</v>
+        <v>6474</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>301.9340868723432</v>
+        <v>306.6773110944108</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>22.65</v>
+        <v>37.75</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>46.32510787332557</v>
+        <v>51.49035336150448</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>12.83014025865579</v>
+        <v>12.34865928908186</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6746978630007758</v>
+        <v>0.8269373065852447</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.0137682093889209</v>
+        <v>0.1572541786013548</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6449</v>
+        <v>6216</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>301.3769564892652</v>
+        <v>301.9340868723432</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>291.5</v>
+        <v>22.65</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>39.90760180472708</v>
+        <v>46.32510787332557</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>19.79459785527214</v>
+        <v>12.83014025865579</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5168744084490084</v>
+        <v>0.6746978630007758</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-10.22976818485874</v>
+        <v>-0.0137682093889209</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6210</v>
+        <v>6449</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>300.0319361480042</v>
+        <v>301.3769564892652</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>19.25</v>
+        <v>291.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>36.92898507301294</v>
+        <v>39.90760180472708</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>26.34485397948453</v>
+        <v>19.79459785527214</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4005478055570337</v>
+        <v>0.5168744084490084</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0576653474599829</v>
+        <v>-10.22976818485874</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6443</v>
+        <v>6210</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>297.2529969299833</v>
+        <v>300.0319361480042</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>30.4</v>
+        <v>19.25</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>29.58686540872964</v>
+        <v>36.92898507301294</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>22.7216572214821</v>
+        <v>26.34485397948453</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5632332686101563</v>
+        <v>0.4005478055570337</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.4442084086317011</v>
+        <v>-0.0576653474599829</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6415</v>
+        <v>6443</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>296.6537263119842</v>
+        <v>297.2529969299833</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>504</v>
+        <v>30.4</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>41.39971486170364</v>
+        <v>29.58686540872964</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>17.24140549251473</v>
+        <v>22.7216572214821</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.6191189539503619</v>
+        <v>0.5632332686101563</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-15.56572591755096</v>
+        <v>-0.4442084086317011</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6291</v>
+        <v>6415</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>290.3049656091561</v>
+        <v>296.6537263119842</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>426</v>
+        <v>504</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>36.07131143593536</v>
+        <v>41.39971486170364</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>18.47634002188281</v>
+        <v>17.24140549251473</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3719868366601902</v>
+        <v>0.6191189539503619</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-15.85427944017878</v>
+        <v>-15.56572591755096</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6227</v>
+        <v>6291</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>289.3874167010006</v>
+        <v>290.3049656091561</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>115</v>
+        <v>426</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>42.61146479576914</v>
+        <v>36.07131143593536</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>13.48635796497865</v>
+        <v>18.47634002188281</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.110912524739454</v>
+        <v>0.3719868366601902</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-1.135944553696299</v>
+        <v>-15.85427944017878</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6170</v>
+        <v>6227</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>285.2598689596613</v>
+        <v>289.3874167010006</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>47.2</v>
+        <v>115</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>25.4253245294142</v>
+        <v>42.61146479576914</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>26.44746242050726</v>
+        <v>13.48635796497865</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.000181478489878</v>
+        <v>1.110912524739454</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.6467603936985183</v>
+        <v>-1.135944553696299</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6205</v>
+        <v>6170</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>282.6801302425092</v>
+        <v>285.2598689596613</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>67</v>
+        <v>47.2</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>37.03642836275981</v>
+        <v>25.4253245294142</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15.55829298820712</v>
+        <v>26.44746242050726</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6377961700090817</v>
+        <v>1.000181478489878</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.9664204903736816</v>
+        <v>-0.6467603936985183</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6222</v>
+        <v>6205</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>279.7603605450328</v>
+        <v>282.6801302425092</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>21.15</v>
+        <v>67</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>54.6520642015935</v>
+        <v>37.03642836275981</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>22.41915188182718</v>
+        <v>15.55829298820712</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.0343395980206655</v>
+        <v>0.6377961700090817</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0503007904795536</v>
+        <v>-0.9664204903736816</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6233</v>
+        <v>6222</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>271.8563897376849</v>
+        <v>279.7603605450328</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>24.55</v>
+        <v>21.15</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>47.16208053021394</v>
+        <v>54.6520642015935</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>13.51294544016343</v>
+        <v>22.41915188182718</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.7818930839771422</v>
+        <v>0.0343395980206655</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.1132829777754213</v>
+        <v>0.0503007904795536</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6485</v>
+        <v>6233</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>268.5040177597102</v>
+        <v>271.8563897376849</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>24.55</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>29.577109942858</v>
+        <v>47.16208053021394</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>21.82191779416263</v>
+        <v>13.51294544016343</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.6924523650318851</v>
+        <v>0.7818930839771422</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,48 +5340,48 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.739297930695475</v>
+        <v>-0.1132829777754213</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6287</v>
+        <v>6485</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>元隆</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>259.61789101409</v>
+        <v>268.5040177597102</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G93" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>75.12890119712088</v>
+        <v>29.577109942858</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v/>
+        <v>21.82191779416263</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3819364013941486</v>
+        <v>0.6924523650318851</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,48 +5393,48 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0007658816175811</v>
+        <v>-0.739297930695475</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6290</v>
+        <v>6287</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>元隆</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>258.6189354268592</v>
+        <v>259.61789101409</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>264</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G94" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>34.32625304955162</v>
+        <v>75.12890119712088</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>14.17990173394929</v>
+        <v/>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5886681728381723</v>
+        <v>0.3819364013941486</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-5.708345820479281</v>
+        <v>0.0007658816175811</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6412</v>
+        <v>6290</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>251.9421652973431</v>
+        <v>258.6189354268592</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>85.7</v>
+        <v>264</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>39.34742427388146</v>
+        <v>34.32625304955162</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>16.11430245911144</v>
+        <v>14.17990173394929</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.523197308037142</v>
+        <v>0.5886681728381723</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.9868624396956251</v>
+        <v>-5.708345820479281</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6228</v>
+        <v>6412</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>249.3009998927801</v>
+        <v>251.9421652973431</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>18.75</v>
+        <v>85.7</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>43.67596251792274</v>
+        <v>39.34742427388146</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>4.939429938458161</v>
+        <v>16.11430245911144</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.0270205274947377</v>
+        <v>0.523197308037142</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0807905722917307</v>
+        <v>-0.9868624396956251</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6188</v>
+        <v>6228</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>246.4108502200656</v>
+        <v>249.3009998927801</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>74.8</v>
+        <v>18.75</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>37.95867794406809</v>
+        <v>43.67596251792274</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>13.89558606090184</v>
+        <v>4.939429938458161</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.472202486212293</v>
+        <v>0.0270205274947377</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.08267838141783571</v>
+        <v>-0.0807905722917307</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6236</v>
+        <v>6188</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>241.1970100550801</v>
+        <v>246.4108502200656</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>0</v>
+        <v>74.8</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>48.11588819305965</v>
+        <v>37.95867794406809</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>6.925534773493278</v>
+        <v>13.89558606090184</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0</v>
+        <v>0.472202486212293</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.3592759676571617</v>
+        <v>-0.08267838141783571</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6246</v>
+        <v>6236</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>240.4795418393643</v>
+        <v>241.1970100550801</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>14.7</v>
+        <v>0</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>39.7864769185487</v>
+        <v>48.11588819305965</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>18.36686201567196</v>
+        <v>6.925534773493278</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.3109534832590961</v>
+        <v>0</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.11211715259704</v>
+        <v>-0.3592759676571617</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6405</v>
+        <v>6246</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>234.880174816889</v>
+        <v>240.4795418393643</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>50</v>
+        <v>14.7</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>33.90908625501451</v>
+        <v>39.7864769185487</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17.58397319528075</v>
+        <v>18.36686201567196</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.4370990145963846</v>
+        <v>0.3109534832590961</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-1.449583842991651</v>
+        <v>-0.11211715259704</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6456</v>
+        <v>6405</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>219.8356426964119</v>
+        <v>234.880174816889</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>50</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>49.57713529980858</v>
+        <v>33.90908625501451</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>16.17694778202851</v>
+        <v>17.58397319528075</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.5893304970744953</v>
+        <v>0.4370990145963846</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.2369851710257853</v>
+        <v>-1.449583842991651</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6237</v>
+        <v>6456</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>216.4015156989825</v>
+        <v>219.8356426964119</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>39.6</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>35.34411069453805</v>
+        <v>49.57713529980858</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>18.83287836788053</v>
+        <v>16.17694778202851</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3057841886974011</v>
+        <v>0.5893304970744953</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.6539062098715138</v>
+        <v>0.2369851710257853</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6272</v>
+        <v>6237</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>206.1696106167857</v>
+        <v>216.4015156989825</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>29.3</v>
+        <v>39.6</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>37.09007898262559</v>
+        <v>35.34411069453805</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>19.56712004352835</v>
+        <v>18.83287836788053</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.3981896662494587</v>
+        <v>0.3057841886974011</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.2240583721700074</v>
+        <v>-0.6539062098715138</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6283</v>
+        <v>6272</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>203.1767664629204</v>
+        <v>206.1696106167857</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>21.95</v>
+        <v>29.3</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>37.9939856892744</v>
+        <v>37.09007898262559</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>15.29386249581966</v>
+        <v>19.56712004352835</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3644610222846219</v>
+        <v>0.3981896662494587</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.2149719907599052</v>
+        <v>-0.2240583721700074</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6167</v>
+        <v>6283</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>201.6567037979502</v>
+        <v>203.1767664629204</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>11.6</v>
+        <v>21.95</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>43.92714031679089</v>
+        <v>37.9939856892744</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>11.25141631113541</v>
+        <v>15.29386249581966</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.3103108520970075</v>
+        <v>0.3644610222846219</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.06542242796007609</v>
+        <v>-0.2149719907599052</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6269</v>
+        <v>6167</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>198.6600354076917</v>
+        <v>201.6567037979502</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>61.6</v>
+        <v>11.6</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>41.12230533062958</v>
+        <v>43.92714031679089</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>16.37680493155352</v>
+        <v>11.25141631113541</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.2507708511367546</v>
+        <v>0.3103108520970075</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-1.418991958147571</v>
+        <v>-0.06542242796007609</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6184</v>
+        <v>6269</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>188.1772606107208</v>
+        <v>198.6600354076917</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>43.1</v>
+        <v>61.6</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>30.02365414535362</v>
+        <v>41.12230533062958</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>33.3626705767425</v>
+        <v>16.37680493155352</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.8270298776838338</v>
+        <v>0.2507708511367546</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0432431572825721</v>
+        <v>-1.418991958147571</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6230</v>
+        <v>6184</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>180.5300564033369</v>
+        <v>188.1772606107208</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>121</v>
+        <v>43.1</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>40.19385929278904</v>
+        <v>30.02365414535362</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>21.62252077776399</v>
+        <v>33.3626705767425</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.077699150629036</v>
+        <v>0.8270298776838338</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.1798202064791549</v>
+        <v>-0.0432431572825721</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6275</v>
+        <v>6230</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>177.9647481120896</v>
+        <v>180.5300564033369</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>47.7</v>
+        <v>121</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>44.5180859544873</v>
+        <v>40.19385929278904</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>12.6285344742437</v>
+        <v>21.62252077776399</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.1959945900581786</v>
+        <v>1.077699150629036</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.2165201571009812</v>
+        <v>-0.1798202064791549</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6203</v>
+        <v>6275</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>175.4582814259402</v>
+        <v>177.9647481120896</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>65.7</v>
+        <v>47.7</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>40.359805341076</v>
+        <v>44.5180859544873</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>13.59138066515863</v>
+        <v>12.6285344742437</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.472962237514521</v>
+        <v>0.1959945900581786</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>1</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.07874576750158201</v>
+        <v>-0.2165201571009812</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6276</v>
+        <v>6203</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>163.1983640182294</v>
+        <v>175.4582814259402</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>22</v>
+        <v>65.7</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>37.49617168842298</v>
+        <v>40.359805341076</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>27.4001095342546</v>
+        <v>13.59138066515863</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4256020704112583</v>
+        <v>0.472962237514521</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>1</v>
@@ -6347,28 +6347,28 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1547130944153207</v>
+        <v>-0.07874576750158201</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6441</v>
+        <v>6276</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>151.2517837507536</v>
+        <v>163.1983640182294</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>22</v>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>44.78058294969814</v>
+        <v>37.49617168842298</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>11.68760726590563</v>
+        <v>27.4001095342546</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.2595798153604101</v>
+        <v>0.4256020704112583</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0117987357137123</v>
+        <v>0.1547130944153207</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6462</v>
+        <v>6441</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>151.0499629701725</v>
+        <v>151.2517837507536</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>103.5</v>
+        <v>22</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>35.75391195274786</v>
+        <v>44.78058294969814</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.99289988144172</v>
+        <v>11.68760726590563</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.3882398657823303</v>
+        <v>0.2595798153604101</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-1.336793916335052</v>
+        <v>0.0117987357137123</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6470</v>
+        <v>6462</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>148.2130949445941</v>
+        <v>151.0499629701725</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>47.75</v>
+        <v>103.5</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>40.58700037931772</v>
+        <v>35.75391195274786</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>11.569078789664</v>
+        <v>16.99289988144172</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.3988571659369287</v>
+        <v>0.3882398657823303</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.2029742970656401</v>
+        <v>-1.336793916335052</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6176</v>
+        <v>6470</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>133.4410292214958</v>
+        <v>148.2130949445941</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>88.2</v>
+        <v>47.75</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>40.32788441718937</v>
+        <v>40.58700037931772</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>17.22112910857189</v>
+        <v>11.569078789664</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.4483375395930938</v>
+        <v>0.3988571659369287</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,62 +6559,115 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.3865701551390161</v>
+        <v>-0.2029742970656401</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
+        <v>6176</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>瑞儀</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>133.4410292214958</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>40.32788441718937</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>17.22112910857189</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.4483375395930938</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.3865701551390161</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
         <v>6194</v>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>育富</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D116" s="2" t="n">
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
         <v>98.23550020290314</v>
       </c>
-      <c r="E116" s="2" t="n">
+      <c r="E117" s="2" t="n">
         <v>30.95</v>
       </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H116" s="2" t="n">
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
         <v>32.03617140508429</v>
       </c>
-      <c r="I116" s="2" t="n">
+      <c r="I117" s="2" t="n">
         <v>17.97028500957192</v>
       </c>
-      <c r="J116" s="2" t="n">
+      <c r="J117" s="2" t="n">
         <v>0.4701117951204391</v>
       </c>
-      <c r="K116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N116" s="2" t="n">
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
         <v>-0.1329032978412301</v>
       </c>
-      <c r="O116" s="2" t="inlineStr">
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
